--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -19,11 +19,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <x:si>
     <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
   </x:si>
   <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_takedown_judo</x:t>
   </x:si>
   <x:si>
@@ -33,70 +78,31 @@
     <x:t>skill_guillotine</x:t>
   </x:si>
   <x:si>
-    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파운딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
   </x:si>
   <x:si>
     <x:t>JiuJitsu</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
     <x:t>StaminaCost</x:t>
   </x:si>
   <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
+    <x:t>skill_uppercut</x:t>
   </x:si>
   <x:si>
     <x:t>skill_ground_pounding</x:t>
@@ -105,22 +111,28 @@
     <x:t>StaminaCostPerSecond</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
     <x:t>cond_wrestling_offense_200</x:t>
   </x:si>
   <x:si>
+    <x:t>cond_jiujitsu_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_150</x:t>
+  </x:si>
+  <x:si>
     <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
   </x:si>
   <x:si>
-    <x:t>cond_jiujitsu_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_150</x:t>
-  </x:si>
-  <x:si>
     <x:t>cond_standing_offense_50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -891,82 +903,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:H35"/>
+  <x:dimension ref="A1:I35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="41.5703125" style="1" customWidth="1"/>
-    <x:col min="4" max="6" width="20.26953125" style="1" customWidth="1"/>
-    <x:col min="7" max="7" width="30.54296875" style="1" customWidth="1"/>
-    <x:col min="8" max="8" width="26.54296875" style="1" customWidth="1"/>
-    <x:col min="9" max="9" width="20" style="1" customWidth="1"/>
-    <x:col min="10" max="12" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="13" max="13" width="15.71484375" style="1" customWidth="1"/>
-    <x:col min="14" max="14" width="17.4296875" style="1" customWidth="1"/>
-    <x:col min="15" max="16384" width="12.54296875" style="1"/>
+    <x:col min="4" max="7" width="20.26953125" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="30.54296875" style="1" customWidth="1"/>
+    <x:col min="9" max="9" width="26.54296875" style="1" customWidth="1"/>
+    <x:col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <x:col min="11" max="13" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="14" max="14" width="15.71484375" style="1" customWidth="1"/>
+    <x:col min="15" max="15" width="17.4296875" style="1" customWidth="1"/>
+    <x:col min="16" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7" ht="13.199999999999999">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8" ht="15.75" customHeight="1">
+    </x:row>
+    <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>22</x:v>
@@ -977,23 +995,26 @@
       <x:c r="F4" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G4" s="1" t="s">
+      <x:c r="G4" s="1">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H4" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="I4" s="4"/>
+    </x:row>
+    <x:row r="5" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>10</x:v>
@@ -1001,22 +1022,25 @@
       <x:c r="F5" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G5" s="1" t="s">
+      <x:c r="G5" s="1">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H5" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="6" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E6" s="1">
         <x:v>3</x:v>
@@ -1024,22 +1048,25 @@
       <x:c r="F6" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="1" t="s">
+      <x:c r="G6" s="1">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H6" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E7" s="1">
         <x:v>4</x:v>
@@ -1047,16 +1074,19 @@
       <x:c r="F7" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G7" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="G7" s="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H7" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>0</x:v>
@@ -1070,13 +1100,38 @@
       <x:c r="F8" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A9" s="5"/>
-      <x:c r="B9" s="5"/>
+      <x:c r="G8" s="1">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H8" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A9" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E9" s="1">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="1">
+        <x:v>0.69999999999999996</x:v>
+      </x:c>
+      <x:c r="H9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1"/>
     <x:row r="11" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11745"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13035"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,27 +19,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+  <x:si>
+    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
+  </x:si>
   <x:si>
     <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
   </x:si>
   <x:si>
+    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>파운딩</x:t>
   </x:si>
   <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
     <x:t>엘보우</x:t>
   </x:si>
   <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
   </x:si>
   <x:si>
     <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
@@ -48,58 +60,76 @@
     <x:t>Name</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
     <x:t>float</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
+    <x:t>None</x:t>
   </x:si>
   <x:si>
     <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
   </x:si>
   <x:si>
     <x:t>CoolTime</x:t>
   </x:si>
   <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_elbow</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_jiujitsu_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsBasicSkill</x:t>
   </x:si>
   <x:si>
     <x:t>skill_uppercut</x:t>
@@ -109,30 +139,6 @@
   </x:si>
   <x:si>
     <x:t>StaminaCostPerSecond</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_wrestling_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_jiujitsu_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -921,67 +927,73 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
+      <x:c r="C2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>33</x:v>
@@ -999,22 +1011,24 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:8" ht="15.75" customHeight="1">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I4" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>10</x:v>
@@ -1026,21 +1040,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8" ht="15.75" customHeight="1">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I5" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E6" s="1">
         <x:v>3</x:v>
@@ -1052,21 +1069,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8" ht="15.75" customHeight="1">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I6" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E7" s="1">
         <x:v>4</x:v>
@@ -1078,18 +1098,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8" ht="15.75" customHeight="1">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I7" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>22</x:v>
@@ -1104,21 +1127,24 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I8" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A9" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A9" s="5" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="1">
         <x:v>2</x:v>
@@ -1130,7 +1156,10 @@
         <x:v>0.69999999999999996</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I9" s="1" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <x:si>
     <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
   </x:si>
@@ -27,78 +27,90 @@
     <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
   </x:si>
   <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseSuccessChance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsBasicSkill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
     <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
   </x:si>
   <x:si>
-    <x:t>파운딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
     <x:t>Wrestling</x:t>
   </x:si>
   <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
     <x:t>CoolTime</x:t>
   </x:si>
   <x:si>
@@ -114,6 +126,12 @@
     <x:t>간결하고 빠른 잽</x:t>
   </x:si>
   <x:si>
+    <x:t>기술 데미지 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_50</x:t>
+  </x:si>
+  <x:si>
     <x:t>cond_wrestling_offense_200</x:t>
   </x:si>
   <x:si>
@@ -126,19 +144,13 @@
     <x:t>cond_standing_offense_150</x:t>
   </x:si>
   <x:si>
-    <x:t>cond_standing_offense_50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsBasicSkill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCostPerSecond</x:t>
   </x:si>
   <x:si>
     <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCostPerSecond</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -909,7 +921,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I35"/>
+  <x:dimension ref="A1:K35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -918,88 +930,107 @@
     <x:col min="4" max="7" width="20.26953125" style="1" customWidth="1"/>
     <x:col min="8" max="8" width="30.54296875" style="1" customWidth="1"/>
     <x:col min="9" max="9" width="26.54296875" style="1" customWidth="1"/>
-    <x:col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <x:col min="11" max="13" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="10" max="10" width="23.28515625" style="1" customWidth="1"/>
+    <x:col min="11" max="11" width="22.85546875" style="1" customWidth="1"/>
+    <x:col min="12" max="13" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
     <x:col min="14" max="14" width="15.71484375" style="1" customWidth="1"/>
     <x:col min="15" max="15" width="17.4296875" style="1" customWidth="1"/>
     <x:col min="16" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9" ht="13.199999999999999">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:11" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J3" s="7" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E4" s="1">
         <x:v>2</x:v>
@@ -1011,24 +1042,30 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I4" s="4" t="b">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J4" s="1">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K4" s="1">
+        <x:v>0.59999999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>10</x:v>
@@ -1040,24 +1077,30 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I5" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J5" s="1">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K5" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E6" s="1">
         <x:v>3</x:v>
@@ -1069,24 +1112,30 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I6" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J6" s="1">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K6" s="1">
+        <x:v>1.3999999999999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E7" s="1">
         <x:v>4</x:v>
@@ -1098,24 +1147,30 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I7" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J7" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K7" s="1">
+        <x:v>1.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="1">
         <x:v>10</x:v>
@@ -1127,24 +1182,30 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I8" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J8" s="1">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E9" s="1">
         <x:v>2</x:v>
@@ -1156,10 +1217,16 @@
         <x:v>0.69999999999999996</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I9" s="1" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="1">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K9" s="1">
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -19,102 +19,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+  <x:si>
+    <x:t>Submission</x:t>
+  </x:si>
   <x:si>
     <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
   </x:si>
   <x:si>
+    <x:t>GroundStrike</x:t>
+  </x:si>
+  <x:si>
     <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
   </x:si>
   <x:si>
+    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsBasicSkill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
     <x:t>엘보우</x:t>
   </x:si>
   <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>파운딩</x:t>
   </x:si>
   <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
     <x:t>어퍼컷</x:t>
   </x:si>
   <x:si>
+    <x:t>DamageMultiplier</x:t>
+  </x:si>
+  <x:si>
     <x:t>RequiredUnlockIds</x:t>
   </x:si>
   <x:si>
     <x:t>BaseSuccessChance</x:t>
   </x:si>
   <x:si>
-    <x:t>DamageMultiplier</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_takedown_judo</x:t>
   </x:si>
   <x:si>
     <x:t>skill_guillotine</x:t>
   </x:si>
   <x:si>
-    <x:t>IsBasicSkill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
     <x:t>bool</x:t>
   </x:si>
   <x:si>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
     <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
   </x:si>
   <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
     <x:t>Category</x:t>
   </x:si>
   <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
+    <x:t>간결하고 빠른 잽</x:t>
   </x:si>
   <x:si>
     <x:t>skill_elbow</x:t>
@@ -123,34 +135,34 @@
     <x:t>skill_jab</x:t>
   </x:si>
   <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
     <x:t>기술 데미지 배율</x:t>
   </x:si>
   <x:si>
+    <x:t>StaminaCostPerSecond</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
+  </x:si>
+  <x:si>
     <x:t>cond_standing_offense_50</x:t>
   </x:si>
   <x:si>
-    <x:t>cond_wrestling_offense_200</x:t>
-  </x:si>
-  <x:si>
     <x:t>cond_jiujitsu_offense_200</x:t>
   </x:si>
   <x:si>
-    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
-  </x:si>
-  <x:si>
     <x:t>cond_standing_offense_150</x:t>
   </x:si>
   <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCostPerSecond</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Takedown</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -921,311 +933,335 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:K35"/>
+  <x:dimension ref="A1:L35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="41.5703125" style="1" customWidth="1"/>
-    <x:col min="4" max="7" width="20.26953125" style="1" customWidth="1"/>
-    <x:col min="8" max="8" width="30.54296875" style="1" customWidth="1"/>
-    <x:col min="9" max="9" width="26.54296875" style="1" customWidth="1"/>
-    <x:col min="10" max="10" width="23.28515625" style="1" customWidth="1"/>
-    <x:col min="11" max="11" width="22.85546875" style="1" customWidth="1"/>
-    <x:col min="12" max="13" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="14" max="14" width="15.71484375" style="1" customWidth="1"/>
-    <x:col min="15" max="15" width="17.4296875" style="1" customWidth="1"/>
-    <x:col min="16" max="16384" width="12.54296875" style="1"/>
+    <x:col min="4" max="8" width="20.26953125" style="1" customWidth="1"/>
+    <x:col min="9" max="9" width="30.54296875" style="1" customWidth="1"/>
+    <x:col min="10" max="10" width="26.54296875" style="1" customWidth="1"/>
+    <x:col min="11" max="11" width="23.28515625" style="1" customWidth="1"/>
+    <x:col min="12" max="12" width="22.85546875" style="1" customWidth="1"/>
+    <x:col min="13" max="14" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="15" max="15" width="15.71484375" style="1" customWidth="1"/>
+    <x:col min="16" max="16" width="17.4296875" style="1" customWidth="1"/>
+    <x:col min="17" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:12" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:11" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:11" s="7" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
+      <x:c r="K3" s="7" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E4" s="1">
+      <x:c r="E4" s="1" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="1">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G4" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G4" s="1">
+      <x:c r="H4" s="1">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="H4" s="1" t="s">
+      <x:c r="I4" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J4" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K4" s="1">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L4" s="1">
+        <x:v>0.59999999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A5" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="I4" s="4" t="b">
+      <x:c r="C5" s="1" t="s">
         <x:v>1</x:v>
-      </x:c>
-      <x:c r="J4" s="1">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="K4" s="1">
-        <x:v>0.59999999999999998</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A5" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E5" s="1">
+      <x:c r="E5" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="1">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F5" s="1">
+      <x:c r="G5" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G5" s="1">
+      <x:c r="H5" s="1">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H5" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I5" s="1" t="b">
+      <x:c r="I5" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J5" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J5" s="1">
+      <x:c r="K5" s="1">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K5" s="1">
+      <x:c r="L5" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="6" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F6" s="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G6" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E6" s="1">
+      <x:c r="I6" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J6" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="1">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L6" s="1">
+        <x:v>1.3999999999999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A7" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F7" s="1">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G7" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F6" s="1">
+      <x:c r="I7" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J7" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="1">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H6" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I6" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="1">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="K6" s="1">
-        <x:v>1.3999999999999999</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A7" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E7" s="1">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F7" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="1">
+      <x:c r="K7" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L7" s="1">
+        <x:v>1.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A8" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="I7" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K7" s="1">
-        <x:v>1.3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A8" s="5" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="1">
+      <x:c r="E8" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F8" s="1">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="1">
+      <x:c r="G8" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G8" s="1">
+      <x:c r="H8" s="1">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H8" s="1" t="s">
+      <x:c r="I8" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J8" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="1">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A9" s="5" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="I8" s="1" t="b">
+      <x:c r="B9" s="5" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F9" s="1">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G9" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J8" s="1">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K8" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A9" s="5" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E9" s="1">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F9" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="1">
+      <x:c r="H9" s="1">
         <x:v>0.69999999999999996</x:v>
       </x:c>
-      <x:c r="H9" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="I9" s="1" t="b">
+      <x:c r="I9" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J9" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J9" s="1">
+      <x:c r="K9" s="1">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="K9" s="1">
+      <x:c r="L9" s="1">
         <x:v>0.5</x:v>
       </x:c>
     </x:row>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -19,150 +19,171 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
+  <x:si>
+    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseSuccessChance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 태클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
+  </x:si>
   <x:si>
     <x:t>Submission</x:t>
   </x:si>
   <x:si>
-    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Takedown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기술 데미지 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchEntry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsBasicSkill</x:t>
   </x:si>
   <x:si>
     <x:t>GroundStrike</x:t>
   </x:si>
   <x:si>
-    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsBasicSkill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파운딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamageMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseSuccessChance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기술 데미지 배율</x:t>
+    <x:t>cond_jiujitsu_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
   </x:si>
   <x:si>
     <x:t>StaminaCostPerSecond</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_wrestling_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_jiujitsu_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Takedown</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -933,7 +954,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:L35"/>
+  <x:dimension ref="A1:L36"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -955,10 +976,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="13.199999999999999">
@@ -966,60 +987,60 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>46</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
         <x:v>30</x:v>
@@ -1028,30 +1049,30 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K3" s="7" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1063,7 +1084,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J4" s="4" t="b">
         <x:v>1</x:v>
@@ -1077,19 +1098,19 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>10</x:v>
@@ -1101,7 +1122,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J5" s="1" t="b">
         <x:v>0</x:v>
@@ -1115,13 +1136,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>19</x:v>
@@ -1139,7 +1160,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J6" s="1" t="b">
         <x:v>0</x:v>
@@ -1153,13 +1174,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>19</x:v>
@@ -1177,7 +1198,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J7" s="1" t="b">
         <x:v>0</x:v>
@@ -1194,16 +1215,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>10</x:v>
@@ -1215,7 +1236,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J8" s="1" t="b">
         <x:v>0</x:v>
@@ -1229,58 +1250,129 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F9" s="1">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G9" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G9" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="H9" s="1">
-        <x:v>0.69999999999999996</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J9" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K9" s="1">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A10" s="5" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F10" s="1">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G10" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="1">
+        <x:v>0.69999999999999996</x:v>
+      </x:c>
+      <x:c r="I10" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J10" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K10" s="1">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="L9" s="1">
+      <x:c r="L10" s="1">
         <x:v>0.5</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="15.75" customHeight="1"/>
-    <x:row r="11" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
-    </x:row>
+    <x:row r="11" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A11" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F11" s="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G11" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I11" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J11" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" s="1">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L11" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A13" s="3"/>
-      <x:c r="B13" s="3"/>
-    </x:row>
-    <x:row r="14" ht="15.75" customHeight="1"/>
+      <x:c r="A13" s="6"/>
+      <x:c r="B13" s="6"/>
+    </x:row>
+    <x:row r="14" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="A14" s="3"/>
+      <x:c r="B14" s="3"/>
+    </x:row>
     <x:row r="15" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A16" s="5"/>
-      <x:c r="B16" s="5"/>
-    </x:row>
+    <x:row r="16" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:2" ht="15.75" customHeight="1">
       <x:c r="A17" s="5"/>
       <x:c r="B17" s="5"/>
@@ -1318,8 +1410,8 @@
       <x:c r="B25" s="5"/>
     </x:row>
     <x:row r="26" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A26" s="6"/>
-      <x:c r="B26" s="6"/>
+      <x:c r="A26" s="5"/>
+      <x:c r="B26" s="5"/>
     </x:row>
     <x:row r="27" spans="1:2" ht="15.75" customHeight="1">
       <x:c r="A27" s="6"/>
@@ -1342,8 +1434,8 @@
       <x:c r="B31" s="6"/>
     </x:row>
     <x:row r="32" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A32" s="3"/>
-      <x:c r="B32" s="3"/>
+      <x:c r="A32" s="6"/>
+      <x:c r="B32" s="6"/>
     </x:row>
     <x:row r="33" spans="1:2" ht="15.75" customHeight="1">
       <x:c r="A33" s="3"/>
@@ -1357,7 +1449,10 @@
       <x:c r="A35" s="3"/>
       <x:c r="B35" s="3"/>
     </x:row>
-    <x:row r="36" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="A36" s="3"/>
+      <x:c r="B36" s="3"/>
+    </x:row>
     <x:row r="37" ht="15.75" customHeight="1"/>
     <x:row r="38" ht="15.75" customHeight="1"/>
     <x:row r="39" ht="15.75" customHeight="1"/>
@@ -2322,6 +2417,7 @@
     <x:row r="998" ht="15.75" customHeight="1"/>
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
+    <x:row r="1001" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -19,138 +19,168 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <x:si>
     <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
   </x:si>
   <x:si>
+    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
   </x:si>
   <x:si>
-    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
   </x:si>
   <x:si>
     <x:t>어퍼컷</x:t>
   </x:si>
   <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파운딩</x:t>
+    <x:t>Escape</x:t>
   </x:si>
   <x:si>
     <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
   </x:si>
   <x:si>
+    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
+  </x:si>
+  <x:si>
     <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
   </x:si>
   <x:si>
+    <x:t>클린치 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 태클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Submission</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Takedown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기술 데미지 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchEntry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_clinch_entry</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
     <x:t>BaseSuccessChance</x:t>
   </x:si>
   <x:si>
-    <x:t>RequiredUnlockIds</x:t>
+    <x:t>skill_takedown_judo</x:t>
   </x:si>
   <x:si>
     <x:t>DamageMultiplier</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 태클</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Submission</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Takedown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기술 데미지 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ClinchEntry</x:t>
+    <x:t>cond_jiujitsu_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundStrike</x:t>
   </x:si>
   <x:si>
     <x:t>skill_uppercut</x:t>
@@ -159,31 +189,13 @@
     <x:t>IsBasicSkill</x:t>
   </x:si>
   <x:si>
-    <x:t>GroundStrike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_jiujitsu_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_wrestling_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
-  </x:si>
-  <x:si>
     <x:t>StaminaCostPerSecond</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -973,51 +985,51 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1">
@@ -1025,54 +1037,54 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>13</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="L3" s="7" t="s">
-        <x:v>14</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1084,7 +1096,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J4" s="4" t="b">
         <x:v>1</x:v>
@@ -1098,19 +1110,19 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>10</x:v>
@@ -1122,7 +1134,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J5" s="1" t="b">
         <x:v>0</x:v>
@@ -1136,19 +1148,19 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>3</x:v>
@@ -1160,7 +1172,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="1" t="b">
         <x:v>0</x:v>
@@ -1174,19 +1186,19 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>4</x:v>
@@ -1212,19 +1224,19 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>10</x:v>
@@ -1236,7 +1248,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="1" t="b">
         <x:v>0</x:v>
@@ -1250,19 +1262,19 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>6</x:v>
@@ -1274,7 +1286,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J9" s="1" t="b">
         <x:v>1</x:v>
@@ -1288,19 +1300,19 @@
     </x:row>
     <x:row r="10" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>2</x:v>
@@ -1312,7 +1324,7 @@
         <x:v>0.69999999999999996</x:v>
       </x:c>
       <x:c r="I10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J10" s="1" t="b">
         <x:v>1</x:v>
@@ -1326,19 +1338,19 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>3</x:v>
@@ -1350,7 +1362,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J11" s="1" t="b">
         <x:v>1</x:v>
@@ -1362,7 +1374,44 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A12" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F12" s="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G12" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="1">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I12" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J12" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L12" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
     <x:row r="13" spans="1:2" ht="15.75" customHeight="1">
       <x:c r="A13" s="6"/>
       <x:c r="B13" s="6"/>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -19,150 +19,180 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="74">
+  <x:si>
+    <x:t>백 컨트롤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
+  </x:si>
   <x:si>
     <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
   </x:si>
   <x:si>
+    <x:t>TargetGroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스윕</x:t>
+  </x:si>
+  <x:si>
     <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
   </x:si>
   <x:si>
-    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파운딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
+    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기술 데미지 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchEntry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Takedown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Submission</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseSuccessChance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 태클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
   </x:si>
   <x:si>
     <x:t>Escape</x:t>
   </x:si>
   <x:si>
-    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
   </x:si>
   <x:si>
     <x:t>클린치 탈출</x:t>
   </x:si>
   <x:si>
-    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 태클</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Submission</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Takedown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기술 데미지 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ClinchEntry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseSuccessChance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamageMultiplier</x:t>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_150</x:t>
   </x:si>
   <x:si>
     <x:t>cond_jiujitsu_offense_200</x:t>
@@ -174,28 +204,43 @@
     <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
   </x:si>
   <x:si>
-    <x:t>cond_wrestling_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_150</x:t>
+    <x:t>skill_uppercut</x:t>
   </x:si>
   <x:si>
     <x:t>GroundStrike</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
     <x:t>IsBasicSkill</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
     <x:t>StaminaCostPerSecond</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ChangeTopBottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하프 가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_sweep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PositionChange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -966,7 +1011,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:L36"/>
+  <x:dimension ref="A1:N36"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -977,7 +1022,7 @@
     <x:col min="10" max="10" width="26.54296875" style="1" customWidth="1"/>
     <x:col min="11" max="11" width="23.28515625" style="1" customWidth="1"/>
     <x:col min="12" max="12" width="22.85546875" style="1" customWidth="1"/>
-    <x:col min="13" max="14" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="14" width="22.5703125" style="1" customWidth="1"/>
     <x:col min="15" max="15" width="15.71484375" style="1" customWidth="1"/>
     <x:col min="16" max="16" width="17.4296875" style="1" customWidth="1"/>
     <x:col min="17" max="16384" width="12.54296875" style="1"/>
@@ -985,106 +1030,118 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="N2" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:14" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="D3" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:12" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="I3" s="7" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J2" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="L2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:12" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1096,7 +1153,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J4" s="4" t="b">
         <x:v>1</x:v>
@@ -1107,22 +1164,28 @@
       <x:c r="L4" s="1">
         <x:v>0.59999999999999998</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="M4" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N4" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>10</x:v>
@@ -1134,7 +1197,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J5" s="1" t="b">
         <x:v>0</x:v>
@@ -1145,22 +1208,28 @@
       <x:c r="L5" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="M5" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N5" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>3</x:v>
@@ -1172,7 +1241,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J6" s="1" t="b">
         <x:v>0</x:v>
@@ -1183,22 +1252,28 @@
       <x:c r="L6" s="1">
         <x:v>1.3999999999999999</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="M6" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N6" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>4</x:v>
@@ -1210,7 +1285,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J7" s="1" t="b">
         <x:v>0</x:v>
@@ -1221,22 +1296,28 @@
       <x:c r="L7" s="1">
         <x:v>1.3</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="M7" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N7" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>10</x:v>
@@ -1248,7 +1329,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J8" s="1" t="b">
         <x:v>0</x:v>
@@ -1259,22 +1340,28 @@
       <x:c r="L8" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="M8" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N8" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>6</x:v>
@@ -1286,7 +1373,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J9" s="1" t="b">
         <x:v>1</x:v>
@@ -1297,22 +1384,28 @@
       <x:c r="L9" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="M9" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N9" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>2</x:v>
@@ -1324,7 +1417,7 @@
         <x:v>0.69999999999999996</x:v>
       </x:c>
       <x:c r="I10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J10" s="1" t="b">
         <x:v>1</x:v>
@@ -1335,22 +1428,28 @@
       <x:c r="L10" s="1">
         <x:v>0.5</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="M10" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N10" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>3</x:v>
@@ -1362,7 +1461,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I11" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J11" s="1" t="b">
         <x:v>1</x:v>
@@ -1373,22 +1472,28 @@
       <x:c r="L11" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="M11" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N11" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>3</x:v>
@@ -1400,7 +1505,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I12" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J12" s="1" t="b">
         <x:v>1</x:v>
@@ -1411,17 +1516,177 @@
       <x:c r="L12" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A13" s="6"/>
-      <x:c r="B13" s="6"/>
-    </x:row>
-    <x:row r="14" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A14" s="3"/>
-      <x:c r="B14" s="3"/>
-    </x:row>
-    <x:row r="15" ht="15.75" customHeight="1"/>
-    <x:row r="16" ht="15.75" customHeight="1"/>
+      <x:c r="M12" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N12" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="A13" s="6" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F13" s="1">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G13" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I13" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J13" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K13" s="1">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L13" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N13" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="A14" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F14" s="1">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G14" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I14" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J14" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K14" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L14" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="N14" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="A15" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F15" s="1">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G15" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="1">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I15" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K15" s="1">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L15" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N15" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="A16" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F16" s="1">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G16" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="1">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I16" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K16" s="1">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L16" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N16" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
     <x:row r="17" spans="1:2" ht="15.75" customHeight="1">
       <x:c r="A17" s="5"/>
       <x:c r="B17" s="5"/>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -19,228 +19,234 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="74">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="76">
+  <x:si>
+    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseSuccessChance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_sweep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기술 데미지 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchEntry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Submission</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Takedown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하프 가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
+  </x:si>
   <x:si>
     <x:t>백 컨트롤</x:t>
   </x:si>
   <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 태클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스윕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundStrike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PositionChange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsBasicSkill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ChangeTopBottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_jiujitsu_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCostPerSecond</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetGroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_halfguard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetGroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파운딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스윕</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_back_control</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기술 데미지 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ClinchEntry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Takedown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Submission</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseSuccessChance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamageMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 태클</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BackControl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_wrestling_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_jiujitsu_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundStrike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsBasicSkill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCostPerSecond</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ChangeTopBottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하프 가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_sweep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PositionChange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1030,18 +1036,18 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:14" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>42</x:v>
@@ -1056,92 +1062,92 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
+      <x:c r="L3" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N3" s="7" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1153,7 +1159,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J4" s="4" t="b">
         <x:v>1</x:v>
@@ -1165,7 +1171,7 @@
         <x:v>0.59999999999999998</x:v>
       </x:c>
       <x:c r="M4" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N4" s="1" t="b">
         <x:v>0</x:v>
@@ -1173,19 +1179,19 @@
     </x:row>
     <x:row r="5" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>10</x:v>
@@ -1197,7 +1203,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J5" s="1" t="b">
         <x:v>0</x:v>
@@ -1209,7 +1215,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M5" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N5" s="1" t="b">
         <x:v>0</x:v>
@@ -1217,19 +1223,19 @@
     </x:row>
     <x:row r="6" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>3</x:v>
@@ -1241,7 +1247,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J6" s="1" t="b">
         <x:v>0</x:v>
@@ -1253,7 +1259,7 @@
         <x:v>1.3999999999999999</x:v>
       </x:c>
       <x:c r="M6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N6" s="1" t="b">
         <x:v>0</x:v>
@@ -1261,19 +1267,19 @@
     </x:row>
     <x:row r="7" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>4</x:v>
@@ -1285,7 +1291,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J7" s="1" t="b">
         <x:v>0</x:v>
@@ -1297,7 +1303,7 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="M7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N7" s="1" t="b">
         <x:v>0</x:v>
@@ -1305,19 +1311,19 @@
     </x:row>
     <x:row r="8" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>10</x:v>
@@ -1329,7 +1335,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J8" s="1" t="b">
         <x:v>0</x:v>
@@ -1341,7 +1347,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N8" s="1" t="b">
         <x:v>0</x:v>
@@ -1349,19 +1355,19 @@
     </x:row>
     <x:row r="9" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>6</x:v>
@@ -1373,7 +1379,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J9" s="1" t="b">
         <x:v>1</x:v>
@@ -1385,7 +1391,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N9" s="1" t="b">
         <x:v>0</x:v>
@@ -1393,19 +1399,19 @@
     </x:row>
     <x:row r="10" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>2</x:v>
@@ -1417,7 +1423,7 @@
         <x:v>0.69999999999999996</x:v>
       </x:c>
       <x:c r="I10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J10" s="1" t="b">
         <x:v>1</x:v>
@@ -1429,7 +1435,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="M10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N10" s="1" t="b">
         <x:v>0</x:v>
@@ -1437,19 +1443,19 @@
     </x:row>
     <x:row r="11" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>3</x:v>
@@ -1461,7 +1467,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J11" s="1" t="b">
         <x:v>1</x:v>
@@ -1473,7 +1479,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N11" s="1" t="b">
         <x:v>0</x:v>
@@ -1481,19 +1487,19 @@
     </x:row>
     <x:row r="12" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>3</x:v>
@@ -1505,7 +1511,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J12" s="1" t="b">
         <x:v>1</x:v>
@@ -1517,7 +1523,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N12" s="1" t="b">
         <x:v>0</x:v>
@@ -1525,16 +1531,16 @@
     </x:row>
     <x:row r="13" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>4</x:v>
@@ -1546,7 +1552,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J13" s="1" t="b">
         <x:v>1</x:v>
@@ -1558,7 +1564,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M13" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N13" s="1" t="b">
         <x:v>0</x:v>
@@ -1566,16 +1572,16 @@
     </x:row>
     <x:row r="14" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>5</x:v>
@@ -1587,7 +1593,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J14" s="1" t="b">
         <x:v>1</x:v>
@@ -1599,7 +1605,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N14" s="1" t="b">
         <x:v>0</x:v>
@@ -1607,16 +1613,16 @@
     </x:row>
     <x:row r="15" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>5</x:v>
@@ -1628,7 +1634,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J15" s="1" t="b">
         <x:v>1</x:v>
@@ -1640,7 +1646,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="N15" s="1" t="b">
         <x:v>0</x:v>
@@ -1648,16 +1654,16 @@
     </x:row>
     <x:row r="16" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>5</x:v>
@@ -1669,7 +1675,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I16" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J16" s="1" t="b">
         <x:v>1</x:v>
@@ -1681,15 +1687,52 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M16" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="N16" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A17" s="5"/>
-      <x:c r="B17" s="5"/>
+    <x:row r="17" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="A17" s="5" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B17" s="5" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F17" s="1">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G17" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I17" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K17" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L17" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="N17" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" spans="1:2" ht="15.75" customHeight="1">
       <x:c r="A18" s="5"/>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13035"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="12795"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,209 +19,212 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="76">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="77">
+  <x:si>
+    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
+  </x:si>
   <x:si>
     <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
   </x:si>
   <x:si>
-    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
+    <x:t>스윕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
   </x:si>
   <x:si>
     <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
   </x:si>
   <x:si>
-    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
+    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기술 데미지 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Submission</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하프 가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Takedown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchEntry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 태클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백 컨트롤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_escape</x:t>
   </x:si>
   <x:si>
     <x:t>DamageMultiplier</x:t>
   </x:si>
   <x:si>
+    <x:t>BaseSuccessChance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_sweep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_guard_pass</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseSuccessChance</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_guillotine</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_back_control</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_sweep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기술 데미지 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ClinchEntry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BackControl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Submission</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Takedown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하프 가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백 컨트롤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 태클</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파운딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스윕</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_uppercut</x:t>
   </x:si>
   <x:si>
+    <x:t>ChangeTopBottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PositionChange</x:t>
+  </x:si>
+  <x:si>
     <x:t>GroundStrike</x:t>
   </x:si>
   <x:si>
-    <x:t>PositionChange</x:t>
-  </x:si>
-  <x:si>
     <x:t>IsBasicSkill</x:t>
   </x:si>
   <x:si>
-    <x:t>ChangeTopBottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>cond_standing_offense_150</x:t>
   </x:si>
   <x:si>
+    <x:t>cond_standing_offense_50</x:t>
+  </x:si>
+  <x:si>
     <x:t>cond_wrestling_offense_200</x:t>
   </x:si>
   <x:si>
@@ -231,22 +234,22 @@
     <x:t>cond_jiujitsu_offense_200</x:t>
   </x:si>
   <x:si>
-    <x:t>cond_standing_offense_50</x:t>
+    <x:t>SubmissionDamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetGroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCostPerSecond</x:t>
   </x:si>
   <x:si>
     <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCostPerSecond</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetGroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_halfguard_pass</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1017,7 +1020,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:N36"/>
+  <x:dimension ref="A1:O36"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -1029,125 +1032,130 @@
     <x:col min="11" max="11" width="23.28515625" style="1" customWidth="1"/>
     <x:col min="12" max="12" width="22.85546875" style="1" customWidth="1"/>
     <x:col min="13" max="14" width="22.5703125" style="1" customWidth="1"/>
-    <x:col min="15" max="15" width="15.71484375" style="1" customWidth="1"/>
-    <x:col min="16" max="16" width="17.4296875" style="1" customWidth="1"/>
+    <x:col min="15" max="16" width="28.4296875" style="1" customWidth="1"/>
     <x:col min="17" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:15" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N2" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="O2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:15" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
         <x:v>17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:14" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J2" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="L2" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="M2" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="N2" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:14" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
+      <x:c r="G3" s="7" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G3" s="7" t="s">
+      <x:c r="I3" s="7" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
+      <x:c r="N3" s="7" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="N3" s="7" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O3" s="7" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1159,7 +1167,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J4" s="4" t="b">
         <x:v>1</x:v>
@@ -1171,27 +1179,30 @@
         <x:v>0.59999999999999998</x:v>
       </x:c>
       <x:c r="M4" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N4" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O4" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A5" s="3" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="N4" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A5" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>10</x:v>
@@ -1203,7 +1214,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J5" s="1" t="b">
         <x:v>0</x:v>
@@ -1215,21 +1226,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M5" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N5" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O5" s="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>47</x:v>
@@ -1259,21 +1273,24 @@
         <x:v>1.3999999999999999</x:v>
       </x:c>
       <x:c r="M6" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N6" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O6" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>47</x:v>
@@ -1291,7 +1308,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J7" s="1" t="b">
         <x:v>0</x:v>
@@ -1303,27 +1320,30 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="M7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N7" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O7" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>10</x:v>
@@ -1335,7 +1355,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J8" s="1" t="b">
         <x:v>0</x:v>
@@ -1347,27 +1367,30 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N8" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>6</x:v>
@@ -1379,7 +1402,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J9" s="1" t="b">
         <x:v>1</x:v>
@@ -1391,18 +1414,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N9" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>21</x:v>
@@ -1423,7 +1449,7 @@
         <x:v>0.69999999999999996</x:v>
       </x:c>
       <x:c r="I10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J10" s="1" t="b">
         <x:v>1</x:v>
@@ -1435,27 +1461,30 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="M10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N10" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O10" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>3</x:v>
@@ -1467,7 +1496,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J11" s="1" t="b">
         <x:v>1</x:v>
@@ -1479,24 +1508,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N11" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O11" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>49</x:v>
@@ -1511,7 +1543,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J12" s="1" t="b">
         <x:v>1</x:v>
@@ -1523,24 +1555,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N12" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O12" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>4</x:v>
@@ -1552,7 +1587,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J13" s="1" t="b">
         <x:v>1</x:v>
@@ -1564,24 +1599,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="N13" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O13" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>5</x:v>
@@ -1593,7 +1631,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J14" s="1" t="b">
         <x:v>1</x:v>
@@ -1605,24 +1643,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N14" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O14" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>5</x:v>
@@ -1634,7 +1675,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J15" s="1" t="b">
         <x:v>1</x:v>
@@ -1646,24 +1687,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="N15" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O15" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>5</x:v>
@@ -1675,7 +1719,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J16" s="1" t="b">
         <x:v>1</x:v>
@@ -1687,21 +1731,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="N16" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O16" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A17" s="5" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B17" s="5" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="B17" s="5" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>49</x:v>
@@ -1716,7 +1763,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J17" s="1" t="b">
         <x:v>1</x:v>
@@ -1728,9 +1775,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N17" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="12795"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13035"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -24,229 +24,229 @@
     <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
   </x:si>
   <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 태클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백 컨트롤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하프 가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Submission</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Takedown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchEntry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기술 데미지 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
     <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseSuccessChance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_sweep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
   </x:si>
   <x:si>
     <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
   </x:si>
   <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
     <x:t>스윕</x:t>
   </x:si>
   <x:si>
-    <x:t>파운딩</x:t>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기술 데미지 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Submission</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하프 가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Takedown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ClinchEntry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BackControl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 태클</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백 컨트롤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamageMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseSuccessChance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_back_control</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_sweep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
+    <x:t>SubmissionDamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_jiujitsu_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_50</x:t>
   </x:si>
   <x:si>
     <x:t>skill_uppercut</x:t>
   </x:si>
   <x:si>
+    <x:t>GroundStrike</x:t>
+  </x:si>
+  <x:si>
     <x:t>ChangeTopBottom</x:t>
   </x:si>
   <x:si>
     <x:t>PositionChange</x:t>
   </x:si>
   <x:si>
-    <x:t>GroundStrike</x:t>
-  </x:si>
-  <x:si>
     <x:t>IsBasicSkill</x:t>
   </x:si>
   <x:si>
-    <x:t>cond_standing_offense_150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_wrestling_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_jiujitsu_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SubmissionDamageMultiplier</x:t>
+    <x:t>StaminaCostPerSecond</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_halfguard_pass</x:t>
   </x:si>
   <x:si>
     <x:t>TargetGroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_halfguard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCostPerSecond</x:t>
   </x:si>
   <x:si>
     <x:t>skill_ground_pounding</x:t>
@@ -1038,107 +1038,107 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:15" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:15" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="N3" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="O3" s="7" t="s">
-        <x:v>71</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
@@ -1146,16 +1146,16 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1167,7 +1167,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J4" s="4" t="b">
         <x:v>1</x:v>
@@ -1179,7 +1179,7 @@
         <x:v>0.59999999999999998</x:v>
       </x:c>
       <x:c r="M4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N4" s="1" t="b">
         <x:v>0</x:v>
@@ -1190,19 +1190,19 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>10</x:v>
@@ -1214,7 +1214,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J5" s="1" t="b">
         <x:v>0</x:v>
@@ -1226,7 +1226,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N5" s="1" t="b">
         <x:v>0</x:v>
@@ -1237,19 +1237,19 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>3</x:v>
@@ -1261,7 +1261,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J6" s="1" t="b">
         <x:v>0</x:v>
@@ -1273,7 +1273,7 @@
         <x:v>1.3999999999999999</x:v>
       </x:c>
       <x:c r="M6" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N6" s="1" t="b">
         <x:v>0</x:v>
@@ -1284,19 +1284,19 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>4</x:v>
@@ -1308,7 +1308,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J7" s="1" t="b">
         <x:v>0</x:v>
@@ -1320,7 +1320,7 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="M7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="1" t="b">
         <x:v>0</x:v>
@@ -1331,19 +1331,19 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>10</x:v>
@@ -1355,7 +1355,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J8" s="1" t="b">
         <x:v>0</x:v>
@@ -1367,7 +1367,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N8" s="1" t="b">
         <x:v>0</x:v>
@@ -1378,19 +1378,19 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>6</x:v>
@@ -1402,10 +1402,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J9" s="1" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K9" s="1">
         <x:v>55</x:v>
@@ -1414,7 +1414,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N9" s="1" t="b">
         <x:v>0</x:v>
@@ -1425,19 +1425,19 @@
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>2</x:v>
@@ -1449,7 +1449,7 @@
         <x:v>0.69999999999999996</x:v>
       </x:c>
       <x:c r="I10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J10" s="1" t="b">
         <x:v>1</x:v>
@@ -1461,7 +1461,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="M10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N10" s="1" t="b">
         <x:v>0</x:v>
@@ -1472,19 +1472,19 @@
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>3</x:v>
@@ -1496,10 +1496,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J11" s="1" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K11" s="1">
         <x:v>60</x:v>
@@ -1508,7 +1508,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N11" s="1" t="b">
         <x:v>0</x:v>
@@ -1519,19 +1519,19 @@
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>3</x:v>
@@ -1543,7 +1543,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J12" s="1" t="b">
         <x:v>1</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N12" s="1" t="b">
         <x:v>0</x:v>
@@ -1566,16 +1566,16 @@
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>4</x:v>
@@ -1587,7 +1587,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J13" s="1" t="b">
         <x:v>1</x:v>
@@ -1599,7 +1599,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N13" s="1" t="b">
         <x:v>0</x:v>
@@ -1610,16 +1610,16 @@
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>5</x:v>
@@ -1631,7 +1631,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J14" s="1" t="b">
         <x:v>1</x:v>
@@ -1643,7 +1643,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N14" s="1" t="b">
         <x:v>0</x:v>
@@ -1654,16 +1654,16 @@
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>5</x:v>
@@ -1675,7 +1675,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J15" s="1" t="b">
         <x:v>1</x:v>
@@ -1687,7 +1687,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N15" s="1" t="b">
         <x:v>0</x:v>
@@ -1698,16 +1698,16 @@
     </x:row>
     <x:row r="16" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>5</x:v>
@@ -1719,7 +1719,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J16" s="1" t="b">
         <x:v>1</x:v>
@@ -1731,7 +1731,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N16" s="1" t="b">
         <x:v>1</x:v>
@@ -1742,16 +1742,16 @@
     </x:row>
     <x:row r="17" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A17" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>5</x:v>
@@ -1763,7 +1763,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J17" s="1" t="b">
         <x:v>1</x:v>
@@ -1775,7 +1775,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N17" s="1" t="b">
         <x:v>0</x:v>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -19,237 +19,243 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="77">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="79">
+  <x:si>
+    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinUseDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxUseDistance</x:t>
+  </x:si>
   <x:si>
     <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
   </x:si>
   <x:si>
+    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스윕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하프 가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Submission</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchEntry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Takedown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기술 데미지 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백 컨트롤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 탈출</x:t>
+  </x:si>
+  <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 태클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 시도</x:t>
+  </x:si>
+  <x:si>
     <x:t>Strike</x:t>
   </x:si>
   <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 태클</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
     <x:t>길로틴 초크</x:t>
   </x:si>
   <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
     <x:t>Escape</x:t>
   </x:si>
   <x:si>
-    <x:t>bool</x:t>
+    <x:t>가드 패스</x:t>
   </x:si>
   <x:si>
     <x:t>클린치 탈출</x:t>
   </x:si>
   <x:si>
-    <x:t>백 컨트롤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하프 가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Submission</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Takedown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ClinchEntry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기술 데미지 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BackControl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
   </x:si>
   <x:si>
     <x:t>skill_clinch_escape</x:t>
   </x:si>
   <x:si>
+    <x:t>DamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_sweep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseSuccessChance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_escape</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_guard_pass</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_ground_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_back_control</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseSuccessChance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamageMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_sweep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파운딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스윕</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PositionChange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundStrike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsBasicSkill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ChangeTopBottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_50</x:t>
   </x:si>
   <x:si>
     <x:t>SubmissionDamageMultiplier</x:t>
   </x:si>
   <x:si>
+    <x:t>cond_standing_offense_150</x:t>
+  </x:si>
+  <x:si>
     <x:t>cond_jiujitsu_offense_200</x:t>
   </x:si>
   <x:si>
-    <x:t>cond_standing_offense_150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
-  </x:si>
-  <x:si>
     <x:t>cond_wrestling_offense_200</x:t>
   </x:si>
   <x:si>
-    <x:t>cond_standing_offense_50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundStrike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ChangeTopBottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PositionChange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsBasicSkill</x:t>
+    <x:t>TargetGroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_halfguard_pass</x:t>
   </x:si>
   <x:si>
     <x:t>StaminaCostPerSecond</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_halfguard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetGroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1020,142 +1026,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:O36"/>
+  <x:dimension ref="A1:Q36"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="41.5703125" style="1" customWidth="1"/>
-    <x:col min="4" max="8" width="20.26953125" style="1" customWidth="1"/>
-    <x:col min="9" max="9" width="30.54296875" style="1" customWidth="1"/>
-    <x:col min="10" max="10" width="26.54296875" style="1" customWidth="1"/>
-    <x:col min="11" max="11" width="23.28515625" style="1" customWidth="1"/>
-    <x:col min="12" max="12" width="22.85546875" style="1" customWidth="1"/>
-    <x:col min="13" max="14" width="22.5703125" style="1" customWidth="1"/>
-    <x:col min="15" max="16" width="28.4296875" style="1" customWidth="1"/>
-    <x:col min="17" max="16384" width="12.54296875" style="1"/>
+    <x:col min="4" max="10" width="20.26953125" style="1" customWidth="1"/>
+    <x:col min="11" max="11" width="30.54296875" style="1" customWidth="1"/>
+    <x:col min="12" max="12" width="26.54296875" style="1" customWidth="1"/>
+    <x:col min="13" max="13" width="23.28515625" style="1" customWidth="1"/>
+    <x:col min="14" max="14" width="22.85546875" style="1" customWidth="1"/>
+    <x:col min="15" max="16" width="22.5703125" style="1" customWidth="1"/>
+    <x:col min="17" max="18" width="28.4296875" style="1" customWidth="1"/>
+    <x:col min="19" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:15" ht="13.199999999999999">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="M1" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N1" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:17" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N2" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O2" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="P2" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="Q2" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:17" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="M2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="N2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="O2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:15" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>71</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K3" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L3" s="7" t="s">
-        <x:v>46</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="M3" s="7" t="s">
-        <x:v>75</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N3" s="7" t="s">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O3" s="7" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="P3" s="7" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="Q3" s="7" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1166,43 +1184,49 @@
       <x:c r="H4" s="1">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="I4" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J4" s="4" t="b">
+      <x:c r="I4" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J4" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L4" s="4" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K4" s="1">
+      <x:c r="M4" s="1">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="L4" s="1">
+      <x:c r="N4" s="1">
         <x:v>0.59999999999999998</x:v>
       </x:c>
-      <x:c r="M4" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N4" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O4" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="O4" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P4" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q4" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>10</x:v>
@@ -1213,43 +1237,49 @@
       <x:c r="H5" s="1">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I5" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="J5" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K5" s="1">
+      <x:c r="I5" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J5" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L5" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="1">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="L5" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M5" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N5" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O5" s="1">
+      <x:c r="N5" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O5" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P5" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5" s="1">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+    <x:row r="6" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>3</x:v>
@@ -1260,43 +1290,49 @@
       <x:c r="H6" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I6" s="1" t="s">
+      <x:c r="I6" s="1">
+        <x:v>0.59999999999999998</x:v>
+      </x:c>
+      <x:c r="J6" s="1">
+        <x:v>0.90000000000000002</x:v>
+      </x:c>
+      <x:c r="K6" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="L6" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="1">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N6" s="1">
+        <x:v>1.3999999999999999</x:v>
+      </x:c>
+      <x:c r="O6" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P6" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A7" s="5" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="J6" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="1">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L6" s="1">
-        <x:v>1.3999999999999999</x:v>
-      </x:c>
-      <x:c r="M6" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N6" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O6" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="5" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>4</x:v>
@@ -1307,43 +1343,49 @@
       <x:c r="H7" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I7" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J7" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="1">
+      <x:c r="I7" s="1">
+        <x:v>0.59999999999999998</x:v>
+      </x:c>
+      <x:c r="J7" s="1">
+        <x:v>1.1000000000000001</x:v>
+      </x:c>
+      <x:c r="K7" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="L7" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L7" s="1">
+      <x:c r="N7" s="1">
         <x:v>1.3</x:v>
       </x:c>
-      <x:c r="M7" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N7" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O7" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="O7" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P7" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>10</x:v>
@@ -1354,43 +1396,49 @@
       <x:c r="H8" s="1">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I8" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="J8" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="1">
+      <x:c r="I8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="L8" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="1">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="L8" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M8" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N8" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O8" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="N8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P8" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>6</x:v>
@@ -1401,43 +1449,49 @@
       <x:c r="H9" s="1">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I9" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J9" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K9" s="1">
+      <x:c r="I9" s="1">
+        <x:v>0.59999999999999998</x:v>
+      </x:c>
+      <x:c r="J9" s="1">
+        <x:v>1.1000000000000001</x:v>
+      </x:c>
+      <x:c r="K9" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L9" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="1">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="L9" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M9" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N9" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O9" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="N9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O9" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P9" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>2</x:v>
@@ -1448,43 +1502,49 @@
       <x:c r="H10" s="1">
         <x:v>0.69999999999999996</x:v>
       </x:c>
-      <x:c r="I10" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J10" s="1" t="b">
+      <x:c r="I10" s="1">
+        <x:v>0.90000000000000002</x:v>
+      </x:c>
+      <x:c r="J10" s="1">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="K10" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L10" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K10" s="1">
+      <x:c r="M10" s="1">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="L10" s="1">
+      <x:c r="N10" s="1">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="M10" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N10" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O10" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="O10" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P10" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>3</x:v>
@@ -1495,43 +1555,49 @@
       <x:c r="H11" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I11" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J11" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="1">
+      <x:c r="I11" s="1">
+        <x:v>0.59999999999999998</x:v>
+      </x:c>
+      <x:c r="J11" s="1">
+        <x:v>0.90000000000000002</x:v>
+      </x:c>
+      <x:c r="K11" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L11" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="1">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="L11" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M11" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N11" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O11" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="N11" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P11" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>3</x:v>
@@ -1542,40 +1608,46 @@
       <x:c r="H12" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I12" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J12" s="1" t="b">
+      <x:c r="I12" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L12" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K12" s="1">
+      <x:c r="M12" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L12" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M12" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N12" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O12" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="N12" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P12" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>4</x:v>
@@ -1586,40 +1658,46 @@
       <x:c r="H13" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I13" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J13" s="1" t="b">
+      <x:c r="I13" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L13" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K13" s="1">
+      <x:c r="M13" s="1">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="L13" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="N13" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O13" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="N13" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="P13" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>5</x:v>
@@ -1630,40 +1708,46 @@
       <x:c r="H14" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I14" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J14" s="1" t="b">
+      <x:c r="I14" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L14" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K14" s="1">
+      <x:c r="M14" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L14" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M14" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N14" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O14" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="N14" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="P14" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>5</x:v>
@@ -1674,40 +1758,46 @@
       <x:c r="H15" s="1">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I15" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J15" s="1" t="b">
+      <x:c r="I15" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L15" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K15" s="1">
+      <x:c r="M15" s="1">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="L15" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N15" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O15" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="N15" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="P15" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q15" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>5</x:v>
@@ -1718,40 +1808,46 @@
       <x:c r="H16" s="1">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I16" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J16" s="1" t="b">
+      <x:c r="I16" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L16" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K16" s="1">
+      <x:c r="M16" s="1">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="L16" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M16" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N16" s="1" t="b">
+      <x:c r="N16" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P16" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O16" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="Q16" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A17" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>5</x:v>
@@ -1762,25 +1858,31 @@
       <x:c r="H17" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I17" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J17" s="1" t="b">
+      <x:c r="I17" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L17" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K17" s="1">
+      <x:c r="M17" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L17" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N17" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O17" s="1">
+      <x:c r="N17" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P17" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q17" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -19,243 +19,264 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="79">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
   <x:si>
     <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
   </x:si>
   <x:si>
+    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCostPerSecond</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetGroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하이킥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미들킥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로우킥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스윕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_kick_high</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ChangeTopBottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PositionChange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxUseDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsBasicSkill</x:t>
+  </x:si>
+  <x:si>
     <x:t>MinUseDistance</x:t>
   </x:si>
   <x:si>
-    <x:t>MaxUseDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
+    <x:t>skill_kick_low</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundStrike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseSuccessChance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_sweep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_kick_middle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
   </x:si>
   <x:si>
     <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
   </x:si>
   <x:si>
-    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파운딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스윕</x:t>
-  </x:si>
-  <x:si>
     <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
   </x:si>
   <x:si>
     <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
   </x:si>
   <x:si>
+    <x:t>하프 가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Submission</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
     <x:t>Category</x:t>
   </x:si>
   <x:si>
-    <x:t>하프 가드 패스</x:t>
-  </x:si>
-  <x:si>
     <x:t>Wrestling</x:t>
   </x:si>
   <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
     <x:t>간결하고 빠른 잽</x:t>
   </x:si>
   <x:si>
-    <x:t>Submission</x:t>
+    <x:t>기술 데미지 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolTime</x:t>
   </x:si>
   <x:si>
     <x:t>skill_jab</x:t>
   </x:si>
   <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
     <x:t>ClinchEntry</x:t>
   </x:si>
   <x:si>
     <x:t>ActionType</x:t>
   </x:si>
   <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
     <x:t>Takedown</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기술 데미지 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BackControl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백 컨트롤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
   </x:si>
   <x:si>
     <x:t>float</x:t>
   </x:si>
   <x:si>
-    <x:t>백 컨트롤</x:t>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 태클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가드 패스</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
+    <x:t>클린치 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 탈출</x:t>
+    <x:t>베이스성공확률</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 태클</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
     <x:t>클린치 시도</x:t>
   </x:si>
   <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamageMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_back_control</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_sweep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseSuccessChance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PositionChange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundStrike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsBasicSkill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ChangeTopBottom</x:t>
+    <x:t>cond_standing_offense_150</x:t>
   </x:si>
   <x:si>
     <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
   </x:si>
   <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_jiujitsu_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmissionDamageMultiplier</x:t>
+  </x:si>
+  <x:si>
     <x:t>cond_standing_offense_50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SubmissionDamageMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_jiujitsu_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_wrestling_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetGroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_halfguard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCostPerSecond</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1044,136 +1065,136 @@
   <x:sheetData>
     <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:17" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="P2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:17" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
+      <x:c r="J3" s="7" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="N3" s="7" t="s">
-        <x:v>55</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="O3" s="7" t="s">
-        <x:v>74</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P3" s="7" t="s">
-        <x:v>67</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Q3" s="7" t="s">
-        <x:v>70</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1191,7 +1212,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K4" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L4" s="4" t="b">
         <x:v>1</x:v>
@@ -1203,7 +1224,7 @@
         <x:v>0.59999999999999998</x:v>
       </x:c>
       <x:c r="O4" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P4" s="1" t="b">
         <x:v>0</x:v>
@@ -1214,19 +1235,19 @@
     </x:row>
     <x:row r="5" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>10</x:v>
@@ -1244,7 +1265,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="L5" s="1" t="b">
         <x:v>0</x:v>
@@ -1256,7 +1277,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O5" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P5" s="1" t="b">
         <x:v>0</x:v>
@@ -1267,19 +1288,19 @@
     </x:row>
     <x:row r="6" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>3</x:v>
@@ -1297,7 +1318,7 @@
         <x:v>0.90000000000000002</x:v>
       </x:c>
       <x:c r="K6" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="L6" s="1" t="b">
         <x:v>0</x:v>
@@ -1309,7 +1330,7 @@
         <x:v>1.3999999999999999</x:v>
       </x:c>
       <x:c r="O6" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P6" s="1" t="b">
         <x:v>0</x:v>
@@ -1320,19 +1341,19 @@
     </x:row>
     <x:row r="7" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>4</x:v>
@@ -1350,7 +1371,7 @@
         <x:v>1.1000000000000001</x:v>
       </x:c>
       <x:c r="K7" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="L7" s="1" t="b">
         <x:v>0</x:v>
@@ -1362,7 +1383,7 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="O7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P7" s="1" t="b">
         <x:v>0</x:v>
@@ -1373,19 +1394,19 @@
     </x:row>
     <x:row r="8" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>10</x:v>
@@ -1403,7 +1424,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="L8" s="1" t="b">
         <x:v>0</x:v>
@@ -1415,7 +1436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P8" s="1" t="b">
         <x:v>0</x:v>
@@ -1426,19 +1447,19 @@
     </x:row>
     <x:row r="9" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>6</x:v>
@@ -1456,7 +1477,7 @@
         <x:v>1.1000000000000001</x:v>
       </x:c>
       <x:c r="K9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L9" s="1" t="b">
         <x:v>0</x:v>
@@ -1468,7 +1489,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P9" s="1" t="b">
         <x:v>0</x:v>
@@ -1479,19 +1500,19 @@
     </x:row>
     <x:row r="10" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>2</x:v>
@@ -1509,7 +1530,7 @@
         <x:v>1.8</x:v>
       </x:c>
       <x:c r="K10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L10" s="1" t="b">
         <x:v>1</x:v>
@@ -1521,7 +1542,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="O10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P10" s="1" t="b">
         <x:v>0</x:v>
@@ -1532,19 +1553,19 @@
     </x:row>
     <x:row r="11" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>3</x:v>
@@ -1562,7 +1583,7 @@
         <x:v>0.90000000000000002</x:v>
       </x:c>
       <x:c r="K11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L11" s="1" t="b">
         <x:v>0</x:v>
@@ -1574,7 +1595,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P11" s="1" t="b">
         <x:v>0</x:v>
@@ -1585,19 +1606,19 @@
     </x:row>
     <x:row r="12" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>3</x:v>
@@ -1615,7 +1636,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L12" s="1" t="b">
         <x:v>1</x:v>
@@ -1627,7 +1648,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P12" s="1" t="b">
         <x:v>0</x:v>
@@ -1638,16 +1659,19 @@
     </x:row>
     <x:row r="13" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>4</x:v>
@@ -1665,7 +1689,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L13" s="1" t="b">
         <x:v>1</x:v>
@@ -1677,7 +1701,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P13" s="1" t="b">
         <x:v>0</x:v>
@@ -1688,16 +1712,19 @@
     </x:row>
     <x:row r="14" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>77</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>5</x:v>
@@ -1715,7 +1742,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L14" s="1" t="b">
         <x:v>1</x:v>
@@ -1727,7 +1754,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="P14" s="1" t="b">
         <x:v>0</x:v>
@@ -1738,16 +1765,19 @@
     </x:row>
     <x:row r="15" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>5</x:v>
@@ -1765,7 +1795,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L15" s="1" t="b">
         <x:v>1</x:v>
@@ -1777,7 +1807,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="P15" s="1" t="b">
         <x:v>0</x:v>
@@ -1788,16 +1818,19 @@
     </x:row>
     <x:row r="16" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>5</x:v>
@@ -1815,7 +1848,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L16" s="1" t="b">
         <x:v>1</x:v>
@@ -1827,7 +1860,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P16" s="1" t="b">
         <x:v>1</x:v>
@@ -1838,16 +1871,19 @@
     </x:row>
     <x:row r="17" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A17" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>5</x:v>
@@ -1865,7 +1901,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L17" s="1" t="b">
         <x:v>1</x:v>
@@ -1877,7 +1913,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P17" s="1" t="b">
         <x:v>0</x:v>
@@ -1886,17 +1922,164 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A18" s="5"/>
-      <x:c r="B18" s="5"/>
-    </x:row>
-    <x:row r="19" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A19" s="5"/>
-      <x:c r="B19" s="5"/>
-    </x:row>
-    <x:row r="20" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A20" s="5"/>
-      <x:c r="B20" s="5"/>
+    <x:row r="18" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A18" s="5" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B18" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F18" s="1">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G18" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I18" s="1">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="J18" s="1">
+        <x:v>2.7999999999999998</x:v>
+      </x:c>
+      <x:c r="K18" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L18" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M18" s="1">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N18" s="1">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="O18" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="P18" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q18" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A19" s="5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B19" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F19" s="1">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G19" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="1">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="I19" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" s="1">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K19" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L19" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M19" s="1">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N19" s="1">
+        <x:v>0.59999999999999998</x:v>
+      </x:c>
+      <x:c r="O19" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="P19" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q19" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A20" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B20" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F20" s="1">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G20" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="1">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I20" s="1">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J20" s="1">
+        <x:v>2.7999999999999998</x:v>
+      </x:c>
+      <x:c r="K20" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L20" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M20" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N20" s="1">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="O20" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="P20" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q20" s="1">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" spans="1:2" ht="15.75" customHeight="1">
       <x:c r="A21" s="5"/>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -21,10 +21,250 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
   <x:si>
+    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘보우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미들킥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하이킥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스윕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로우킥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_sweep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseSuccessChance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_kick_middle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Takedown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기술 데미지 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchEntry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하프 가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Submission</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ChangeTopBottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PositionChange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxUseDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsBasicSkill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_kick_low</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinUseDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundStrike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_kick_high</x:t>
+  </x:si>
+  <x:si>
     <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
   </x:si>
   <x:si>
-    <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백 컨트롤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 태클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_jiujitsu_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmissionDamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
   </x:si>
   <x:si>
     <x:t>skill_ground_pounding</x:t>
@@ -33,250 +273,10 @@
     <x:t>StaminaCostPerSecond</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
     <x:t>TargetGroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_halfguard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하이킥</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미들킥</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로우킥</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스윕</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파운딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘보우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_kick_high</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ChangeTopBottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PositionChange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxUseDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsBasicSkill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinUseDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_kick_low</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundStrike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_back_control</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseSuccessChance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_sweep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamageMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_kick_middle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하프 가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Submission</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기술 데미지 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ClinchEntry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BackControl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Takedown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백 컨트롤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 태클</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_wrestling_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_jiujitsu_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SubmissionDamageMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_50</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1065,136 +1065,136 @@
   <x:sheetData>
     <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:17" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="P2" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Q2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:17" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>52</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="O3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="P3" s="7" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N3" s="7" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="O3" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="P3" s="7" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="Q3" s="7" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1212,7 +1212,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K4" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L4" s="4" t="b">
         <x:v>1</x:v>
@@ -1224,7 +1224,7 @@
         <x:v>0.59999999999999998</x:v>
       </x:c>
       <x:c r="O4" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P4" s="1" t="b">
         <x:v>0</x:v>
@@ -1235,16 +1235,16 @@
     </x:row>
     <x:row r="5" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>43</x:v>
@@ -1265,7 +1265,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K5" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="L5" s="1" t="b">
         <x:v>0</x:v>
@@ -1277,7 +1277,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O5" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P5" s="1" t="b">
         <x:v>0</x:v>
@@ -1291,16 +1291,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>3</x:v>
@@ -1318,7 +1318,7 @@
         <x:v>0.90000000000000002</x:v>
       </x:c>
       <x:c r="K6" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="L6" s="1" t="b">
         <x:v>0</x:v>
@@ -1330,7 +1330,7 @@
         <x:v>1.3999999999999999</x:v>
       </x:c>
       <x:c r="O6" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P6" s="1" t="b">
         <x:v>0</x:v>
@@ -1341,19 +1341,19 @@
     </x:row>
     <x:row r="7" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>4</x:v>
@@ -1371,7 +1371,7 @@
         <x:v>1.1000000000000001</x:v>
       </x:c>
       <x:c r="K7" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="L7" s="1" t="b">
         <x:v>0</x:v>
@@ -1383,7 +1383,7 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="O7" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P7" s="1" t="b">
         <x:v>0</x:v>
@@ -1394,19 +1394,19 @@
     </x:row>
     <x:row r="8" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>10</x:v>
@@ -1424,7 +1424,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="L8" s="1" t="b">
         <x:v>0</x:v>
@@ -1436,7 +1436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O8" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P8" s="1" t="b">
         <x:v>0</x:v>
@@ -1447,19 +1447,19 @@
     </x:row>
     <x:row r="9" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>6</x:v>
@@ -1477,7 +1477,7 @@
         <x:v>1.1000000000000001</x:v>
       </x:c>
       <x:c r="K9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L9" s="1" t="b">
         <x:v>0</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P9" s="1" t="b">
         <x:v>0</x:v>
@@ -1500,19 +1500,19 @@
     </x:row>
     <x:row r="10" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>2</x:v>
@@ -1530,7 +1530,7 @@
         <x:v>1.8</x:v>
       </x:c>
       <x:c r="K10" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L10" s="1" t="b">
         <x:v>1</x:v>
@@ -1542,7 +1542,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="O10" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P10" s="1" t="b">
         <x:v>0</x:v>
@@ -1553,19 +1553,19 @@
     </x:row>
     <x:row r="11" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>3</x:v>
@@ -1583,7 +1583,7 @@
         <x:v>0.90000000000000002</x:v>
       </x:c>
       <x:c r="K11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L11" s="1" t="b">
         <x:v>0</x:v>
@@ -1595,7 +1595,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P11" s="1" t="b">
         <x:v>0</x:v>
@@ -1606,19 +1606,19 @@
     </x:row>
     <x:row r="12" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>3</x:v>
@@ -1636,7 +1636,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L12" s="1" t="b">
         <x:v>1</x:v>
@@ -1648,7 +1648,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P12" s="1" t="b">
         <x:v>0</x:v>
@@ -1659,19 +1659,19 @@
     </x:row>
     <x:row r="13" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>4</x:v>
@@ -1689,7 +1689,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L13" s="1" t="b">
         <x:v>1</x:v>
@@ -1701,7 +1701,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="P13" s="1" t="b">
         <x:v>0</x:v>
@@ -1712,19 +1712,19 @@
     </x:row>
     <x:row r="14" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>5</x:v>
@@ -1742,7 +1742,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L14" s="1" t="b">
         <x:v>1</x:v>
@@ -1754,7 +1754,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="P14" s="1" t="b">
         <x:v>0</x:v>
@@ -1765,19 +1765,19 @@
     </x:row>
     <x:row r="15" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>5</x:v>
@@ -1795,7 +1795,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L15" s="1" t="b">
         <x:v>1</x:v>
@@ -1807,7 +1807,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="P15" s="1" t="b">
         <x:v>0</x:v>
@@ -1818,19 +1818,19 @@
     </x:row>
     <x:row r="16" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>5</x:v>
@@ -1848,7 +1848,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L16" s="1" t="b">
         <x:v>1</x:v>
@@ -1860,7 +1860,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="P16" s="1" t="b">
         <x:v>1</x:v>
@@ -1871,19 +1871,19 @@
     </x:row>
     <x:row r="17" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A17" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>5</x:v>
@@ -1901,7 +1901,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L17" s="1" t="b">
         <x:v>1</x:v>
@@ -1913,7 +1913,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P17" s="1" t="b">
         <x:v>0</x:v>
@@ -1924,19 +1924,19 @@
     </x:row>
     <x:row r="18" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A18" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F18" s="1">
         <x:v>8</x:v>
@@ -1954,7 +1954,7 @@
         <x:v>2.7999999999999998</x:v>
       </x:c>
       <x:c r="K18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L18" s="1" t="b">
         <x:v>1</x:v>
@@ -1966,7 +1966,7 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="O18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P18" s="1" t="b">
         <x:v>0</x:v>
@@ -1977,19 +1977,19 @@
     </x:row>
     <x:row r="19" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A19" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F19" s="1">
         <x:v>5</x:v>
@@ -2007,10 +2007,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K19" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L19" s="1" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M19" s="1">
         <x:v>60</x:v>
@@ -2019,7 +2019,7 @@
         <x:v>0.59999999999999998</x:v>
       </x:c>
       <x:c r="O19" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P19" s="1" t="b">
         <x:v>0</x:v>
@@ -2030,19 +2030,19 @@
     </x:row>
     <x:row r="20" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A20" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F20" s="1">
         <x:v>6</x:v>
@@ -2060,10 +2060,10 @@
         <x:v>2.7999999999999998</x:v>
       </x:c>
       <x:c r="K20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L20" s="1" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M20" s="1">
         <x:v>50</x:v>
@@ -2072,7 +2072,7 @@
         <x:v>1.8</x:v>
       </x:c>
       <x:c r="O20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P20" s="1" t="b">
         <x:v>0</x:v>
